--- a/data/processed/harmonization/Carbon__Total_carbon/10.15485_3374640/10.15485_3374640_soil_Carbon__Total_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Total_carbon/10.15485_3374640/10.15485_3374640_soil_Carbon__Total_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="59" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Grass Bay:1:0-2</t>
+          <t>Grass Bay:1:1:0-2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Grass Bay:1:2-4</t>
+          <t>Grass Bay:1:1:2-4</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Grass Bay:1:4-6</t>
+          <t>Grass Bay:1:1:4-6</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Grass Bay:1:6-8</t>
+          <t>Grass Bay:1:1:6-8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Grass Bay:1:8-10</t>
+          <t>Grass Bay:1:1:8-10</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Grass Bay:1:10-12</t>
+          <t>Grass Bay:1:1:10-12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Grass Bay:1:12-15</t>
+          <t>Grass Bay:1:1:12-15</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Grass Bay:1:15-20</t>
+          <t>Grass Bay:1:1:15-20</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Grass Bay:1:20-25</t>
+          <t>Grass Bay:1:1:20-25</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:0-1</t>
+          <t>Moxely Marsh Center:2:1:0-1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:1-2</t>
+          <t>Moxely Marsh Center:2:1:1-2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:2-3</t>
+          <t>Moxely Marsh Center:2:1:2-3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:3-4</t>
+          <t>Moxely Marsh Center:2:1:3-4</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:4-5</t>
+          <t>Moxely Marsh Center:2:1:4-5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:5-7</t>
+          <t>Moxely Marsh Center:2:1:5-7</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:7-9</t>
+          <t>Moxely Marsh Center:2:1:7-9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:9-11</t>
+          <t>Moxely Marsh Center:2:1:9-11</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:11-13</t>
+          <t>Moxely Marsh Center:2:1:11-13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:13-15</t>
+          <t>Moxely Marsh Center:2:1:13-15</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:15-17</t>
+          <t>Moxely Marsh Center:2:1:15-17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:17-19</t>
+          <t>Moxely Marsh Center:2:1:17-19</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:19-21</t>
+          <t>Moxely Marsh Center:2:1:19-21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:21-23</t>
+          <t>Moxely Marsh Center:2:1:21-23</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:23-25</t>
+          <t>Moxely Marsh Center:2:1:23-25</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:25-27</t>
+          <t>Moxely Marsh Center:2:1:25-27</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:2:27-28.5</t>
+          <t>Moxely Marsh Center:2:1:27-28.5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:0-1</t>
+          <t>Moxely Marsh Center:2:2:0-1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:1-2</t>
+          <t>Moxely Marsh Center:2:2:1-2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:2-3</t>
+          <t>Moxely Marsh Center:2:2:2-3</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:3-4</t>
+          <t>Moxely Marsh Center:2:2:3-4</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:4-5</t>
+          <t>Moxely Marsh Center:2:2:4-5</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:5-7</t>
+          <t>Moxely Marsh Center:2:2:5-7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:7-9</t>
+          <t>Moxely Marsh Center:2:2:7-9</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:9-11</t>
+          <t>Moxely Marsh Center:2:2:9-11</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:11-13</t>
+          <t>Moxely Marsh Center:2:2:11-13</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:13-15</t>
+          <t>Moxely Marsh Center:2:2:13-15</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:15-17</t>
+          <t>Moxely Marsh Center:2:2:15-17</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:17-19</t>
+          <t>Moxely Marsh Center:2:2:17-19</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:19-21</t>
+          <t>Moxely Marsh Center:2:2:19-21</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:21-23</t>
+          <t>Moxely Marsh Center:2:2:21-23</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:23-25</t>
+          <t>Moxely Marsh Center:2:2:23-25</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:25-27</t>
+          <t>Moxely Marsh Center:2:2:25-27</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:27-29</t>
+          <t>Moxely Marsh Center:2:2:27-29</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:29-31</t>
+          <t>Moxely Marsh Center:2:2:29-31</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:31-33</t>
+          <t>Moxely Marsh Center:2:2:31-33</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Moxely Marsh Center:3:33-35</t>
+          <t>Moxely Marsh Center:2:2:33-35</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:0-1</t>
+          <t>Standing Rush Center Point:3:1:0-1</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:1-2</t>
+          <t>Standing Rush Center Point:3:1:1-2</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:2-3</t>
+          <t>Standing Rush Center Point:3:1:2-3</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:3-4</t>
+          <t>Standing Rush Center Point:3:1:3-4</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:4-5</t>
+          <t>Standing Rush Center Point:3:1:4-5</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:5-7</t>
+          <t>Standing Rush Center Point:3:1:5-7</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:7-9</t>
+          <t>Standing Rush Center Point:3:1:7-9</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:9-11</t>
+          <t>Standing Rush Center Point:3:1:9-11</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:11-13</t>
+          <t>Standing Rush Center Point:3:1:11-13</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:13-15</t>
+          <t>Standing Rush Center Point:3:1:13-15</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:15-17</t>
+          <t>Standing Rush Center Point:3:1:15-17</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:17-19</t>
+          <t>Standing Rush Center Point:3:1:17-19</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:19-21</t>
+          <t>Standing Rush Center Point:3:1:19-21</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:21-23</t>
+          <t>Standing Rush Center Point:3:1:21-23</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:23-25</t>
+          <t>Standing Rush Center Point:3:1:23-25</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:25-27</t>
+          <t>Standing Rush Center Point:3:1:25-27</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:27-29</t>
+          <t>Standing Rush Center Point:3:1:27-29</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:4:29-31</t>
+          <t>Standing Rush Center Point:3:1:29-31</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:0-1</t>
+          <t>Standing Rush Center Point:3:2:0-1</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:1-2</t>
+          <t>Standing Rush Center Point:3:2:1-2</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:2-3</t>
+          <t>Standing Rush Center Point:3:2:2-3</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:3-4</t>
+          <t>Standing Rush Center Point:3:2:3-4</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:4-5</t>
+          <t>Standing Rush Center Point:3:2:4-5</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:5-7</t>
+          <t>Standing Rush Center Point:3:2:5-7</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:7-9</t>
+          <t>Standing Rush Center Point:3:2:7-9</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:9-11</t>
+          <t>Standing Rush Center Point:3:2:9-11</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:11-13</t>
+          <t>Standing Rush Center Point:3:2:11-13</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:13-15</t>
+          <t>Standing Rush Center Point:3:2:13-15</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:15-17</t>
+          <t>Standing Rush Center Point:3:2:15-17</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:17-19</t>
+          <t>Standing Rush Center Point:3:2:17-19</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:19-21</t>
+          <t>Standing Rush Center Point:3:2:19-21</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:21-23</t>
+          <t>Standing Rush Center Point:3:2:21-23</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:23-25</t>
+          <t>Standing Rush Center Point:3:2:23-25</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:25-27</t>
+          <t>Standing Rush Center Point:3:2:25-27</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:27-29</t>
+          <t>Standing Rush Center Point:3:2:27-29</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:29-31</t>
+          <t>Standing Rush Center Point:3:2:29-31</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:31-33</t>
+          <t>Standing Rush Center Point:3:2:31-33</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:33-35</t>
+          <t>Standing Rush Center Point:3:2:33-35</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Standing Rush Center Point:5:35-38.5</t>
+          <t>Standing Rush Center Point:3:2:35-38.5</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:0-1</t>
+          <t>Forder Bridge River Access:4:1:0-1</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:1-2</t>
+          <t>Forder Bridge River Access:4:1:1-2</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:2-3</t>
+          <t>Forder Bridge River Access:4:1:2-3</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:3-4</t>
+          <t>Forder Bridge River Access:4:1:3-4</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:4-5</t>
+          <t>Forder Bridge River Access:4:1:4-5</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:5-7</t>
+          <t>Forder Bridge River Access:4:1:5-7</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:7-9</t>
+          <t>Forder Bridge River Access:4:1:7-9</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:9-11</t>
+          <t>Forder Bridge River Access:4:1:9-11</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:11-13</t>
+          <t>Forder Bridge River Access:4:1:11-13</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:13-15</t>
+          <t>Forder Bridge River Access:4:1:13-15</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:15-17</t>
+          <t>Forder Bridge River Access:4:1:15-17</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:6:17-19</t>
+          <t>Forder Bridge River Access:4:1:17-19</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:7:0-1</t>
+          <t>Forder Bridge River Access:4:2:0-1</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:7:1-2</t>
+          <t>Forder Bridge River Access:4:2:1-2</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:7:2-3</t>
+          <t>Forder Bridge River Access:4:2:2-3</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:7:3-4</t>
+          <t>Forder Bridge River Access:4:2:3-4</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:7:4-5</t>
+          <t>Forder Bridge River Access:4:2:4-5</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:7:5-7</t>
+          <t>Forder Bridge River Access:4:2:5-7</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:7:7-9</t>
+          <t>Forder Bridge River Access:4:2:7-9</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:7:9-11</t>
+          <t>Forder Bridge River Access:4:2:9-11</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Forder Bridge River Access:7:11-12.5</t>
+          <t>Forder Bridge River Access:4:2:11-12.5</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:0-1</t>
+          <t>Kalida Fish and Game:5:1:0-1</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:1-2</t>
+          <t>Kalida Fish and Game:5:1:1-2</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:2-3</t>
+          <t>Kalida Fish and Game:5:1:2-3</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:3-4</t>
+          <t>Kalida Fish and Game:5:1:3-4</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:4-5</t>
+          <t>Kalida Fish and Game:5:1:4-5</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:5-7</t>
+          <t>Kalida Fish and Game:5:1:5-7</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:7-9</t>
+          <t>Kalida Fish and Game:5:1:7-9</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:9-11</t>
+          <t>Kalida Fish and Game:5:1:9-11</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:11-13</t>
+          <t>Kalida Fish and Game:5:1:11-13</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:13-15</t>
+          <t>Kalida Fish and Game:5:1:13-15</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:15-17</t>
+          <t>Kalida Fish and Game:5:1:15-17</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:17-19</t>
+          <t>Kalida Fish and Game:5:1:17-19</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:8:19-21</t>
+          <t>Kalida Fish and Game:5:1:19-21</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:0-1</t>
+          <t>Kalida Fish and Game:5:2:0-1</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:1-2</t>
+          <t>Kalida Fish and Game:5:2:1-2</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:2-3</t>
+          <t>Kalida Fish and Game:5:2:2-3</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:3-4</t>
+          <t>Kalida Fish and Game:5:2:3-4</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:4-5</t>
+          <t>Kalida Fish and Game:5:2:4-5</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:5-7</t>
+          <t>Kalida Fish and Game:5:2:5-7</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:7-9</t>
+          <t>Kalida Fish and Game:5:2:7-9</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:9-11</t>
+          <t>Kalida Fish and Game:5:2:9-11</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:11-13</t>
+          <t>Kalida Fish and Game:5:2:11-13</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:13-16</t>
+          <t>Kalida Fish and Game:5:2:13-16</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:16-18</t>
+          <t>Kalida Fish and Game:5:2:16-18</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Kalida Fish and Game:9:18-20</t>
+          <t>Kalida Fish and Game:5:2:18-20</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:0-1</t>
+          <t>St Joseph River Wildlife Area:6:1:0-1</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:1-2</t>
+          <t>St Joseph River Wildlife Area:6:1:1-2</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:2-3</t>
+          <t>St Joseph River Wildlife Area:6:1:2-3</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:3-4</t>
+          <t>St Joseph River Wildlife Area:6:1:3-4</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:4-5</t>
+          <t>St Joseph River Wildlife Area:6:1:4-5</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:5-7</t>
+          <t>St Joseph River Wildlife Area:6:1:5-7</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:7-9</t>
+          <t>St Joseph River Wildlife Area:6:1:7-9</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:9-11</t>
+          <t>St Joseph River Wildlife Area:6:1:9-11</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:11-13</t>
+          <t>St Joseph River Wildlife Area:6:1:11-13</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:13-15</t>
+          <t>St Joseph River Wildlife Area:6:1:13-15</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:15-17</t>
+          <t>St Joseph River Wildlife Area:6:1:15-17</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:17-19</t>
+          <t>St Joseph River Wildlife Area:6:1:17-19</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:10:19-22</t>
+          <t>St Joseph River Wildlife Area:6:1:19-22</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:0-1</t>
+          <t>St Joseph River Wildlife Area:6:2:0-1</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:1-2</t>
+          <t>St Joseph River Wildlife Area:6:2:1-2</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:2-3</t>
+          <t>St Joseph River Wildlife Area:6:2:2-3</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:3-4</t>
+          <t>St Joseph River Wildlife Area:6:2:3-4</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:4-5</t>
+          <t>St Joseph River Wildlife Area:6:2:4-5</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:5-7</t>
+          <t>St Joseph River Wildlife Area:6:2:5-7</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:7-9</t>
+          <t>St Joseph River Wildlife Area:6:2:7-9</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:9-11</t>
+          <t>St Joseph River Wildlife Area:6:2:9-11</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:11-13</t>
+          <t>St Joseph River Wildlife Area:6:2:11-13</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:13-15</t>
+          <t>St Joseph River Wildlife Area:6:2:13-15</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:15-17</t>
+          <t>St Joseph River Wildlife Area:6:2:15-17</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:17-19</t>
+          <t>St Joseph River Wildlife Area:6:2:17-19</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:19-21</t>
+          <t>St Joseph River Wildlife Area:6:2:19-21</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>St Joseph River Wildlife Area:11:21-23</t>
+          <t>St Joseph River Wildlife Area:6:2:21-23</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:0-1</t>
+          <t>Winous Point West:7:1:0-1</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:1-2</t>
+          <t>Winous Point West:7:1:1-2</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:2-3</t>
+          <t>Winous Point West:7:1:2-3</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:3-4</t>
+          <t>Winous Point West:7:1:3-4</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:4-5</t>
+          <t>Winous Point West:7:1:4-5</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:5-7</t>
+          <t>Winous Point West:7:1:5-7</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:7-9</t>
+          <t>Winous Point West:7:1:7-9</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:9-11</t>
+          <t>Winous Point West:7:1:9-11</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:11-13</t>
+          <t>Winous Point West:7:1:11-13</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:13-15</t>
+          <t>Winous Point West:7:1:13-15</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:15-17</t>
+          <t>Winous Point West:7:1:15-17</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:17-19</t>
+          <t>Winous Point West:7:1:17-19</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:19-21</t>
+          <t>Winous Point West:7:1:19-21</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:21-23</t>
+          <t>Winous Point West:7:1:21-23</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:23-25</t>
+          <t>Winous Point West:7:1:23-25</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:25-27</t>
+          <t>Winous Point West:7:1:25-27</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:27-29</t>
+          <t>Winous Point West:7:1:27-29</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:29-31</t>
+          <t>Winous Point West:7:1:29-31</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:31-33</t>
+          <t>Winous Point West:7:1:31-33</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:33-35</t>
+          <t>Winous Point West:7:1:33-35</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:35-37</t>
+          <t>Winous Point West:7:1:35-37</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:37-39</t>
+          <t>Winous Point West:7:1:37-39</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:39-41</t>
+          <t>Winous Point West:7:1:39-41</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9930,12 +9930,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:41-43</t>
+          <t>Winous Point West:7:1:41-43</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:43-45</t>
+          <t>Winous Point West:7:1:43-45</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:12:45-48</t>
+          <t>Winous Point West:7:1:45-48</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:0-1</t>
+          <t>Winous Point West:7:2:0-1</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:1-2</t>
+          <t>Winous Point West:7:2:1-2</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:2-3</t>
+          <t>Winous Point West:7:2:2-3</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:3-4</t>
+          <t>Winous Point West:7:2:3-4</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:4-5.5</t>
+          <t>Winous Point West:7:2:4-5.5</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:5.5-7.5</t>
+          <t>Winous Point West:7:2:5.5-7.5</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10398,12 +10398,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:7.5-9.5</t>
+          <t>Winous Point West:7:2:7.5-9.5</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:9.5-11.5</t>
+          <t>Winous Point West:7:2:9.5-11.5</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:11.5-13.5</t>
+          <t>Winous Point West:7:2:11.5-13.5</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:13.5-15.5</t>
+          <t>Winous Point West:7:2:13.5-15.5</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:15.5-17.5</t>
+          <t>Winous Point West:7:2:15.5-17.5</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:17.5-19.5</t>
+          <t>Winous Point West:7:2:17.5-19.5</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:19.5-21.5</t>
+          <t>Winous Point West:7:2:19.5-21.5</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:21.5-23.5</t>
+          <t>Winous Point West:7:2:21.5-23.5</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:23.5-25.5</t>
+          <t>Winous Point West:7:2:23.5-25.5</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:25.5-27.5</t>
+          <t>Winous Point West:7:2:25.5-27.5</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:27.5-29.5</t>
+          <t>Winous Point West:7:2:27.5-29.5</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:29.5-31.5</t>
+          <t>Winous Point West:7:2:29.5-31.5</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:31.5-33.5</t>
+          <t>Winous Point West:7:2:31.5-33.5</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:33.5-35.5</t>
+          <t>Winous Point West:7:2:33.5-35.5</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:35.5-37.5</t>
+          <t>Winous Point West:7:2:35.5-37.5</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -11178,12 +11178,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:37.5-39.5</t>
+          <t>Winous Point West:7:2:37.5-39.5</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:39.5-41.5</t>
+          <t>Winous Point West:7:2:39.5-41.5</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:41.5-43.5</t>
+          <t>Winous Point West:7:2:41.5-43.5</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11334,12 +11334,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Winous Point West:13:43.5-45.5</t>
+          <t>Winous Point West:7:2:43.5-45.5</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:0-1</t>
+          <t>Metzgers Gate:8:1:0-1</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:1-2</t>
+          <t>Metzgers Gate:8:1:1-2</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:2-3</t>
+          <t>Metzgers Gate:8:1:2-3</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11542,12 +11542,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:3-4</t>
+          <t>Metzgers Gate:8:1:3-4</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:4-5</t>
+          <t>Metzgers Gate:8:1:4-5</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:5-7</t>
+          <t>Metzgers Gate:8:1:5-7</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:7-9</t>
+          <t>Metzgers Gate:8:1:7-9</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11750,12 +11750,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:9-11</t>
+          <t>Metzgers Gate:8:1:9-11</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:11-13</t>
+          <t>Metzgers Gate:8:1:11-13</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:13-15</t>
+          <t>Metzgers Gate:8:1:13-15</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:14:15-17</t>
+          <t>Metzgers Gate:8:1:15-17</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:0-1</t>
+          <t>Metzgers Gate:8:2:0-1</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:1-2</t>
+          <t>Metzgers Gate:8:2:1-2</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:2-3</t>
+          <t>Metzgers Gate:8:2:2-3</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:3-4</t>
+          <t>Metzgers Gate:8:2:3-4</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -12166,12 +12166,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:4-5</t>
+          <t>Metzgers Gate:8:2:4-5</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:5-7</t>
+          <t>Metzgers Gate:8:2:5-7</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12270,12 +12270,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:7-9</t>
+          <t>Metzgers Gate:8:2:7-9</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:9-11</t>
+          <t>Metzgers Gate:8:2:9-11</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12374,12 +12374,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:11-13</t>
+          <t>Metzgers Gate:8:2:11-13</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:13-15</t>
+          <t>Metzgers Gate:8:2:13-15</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12478,12 +12478,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:15-17</t>
+          <t>Metzgers Gate:8:2:15-17</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:17-18</t>
+          <t>Metzgers Gate:8:2:17-18</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:18-20</t>
+          <t>Metzgers Gate:8:2:18-20</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Metzgers Gate:15:20-21</t>
+          <t>Metzgers Gate:8:2:20-21</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:0-1</t>
+          <t>North Lilly:9:1:0-1</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12738,12 +12738,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:1-2</t>
+          <t>North Lilly:9:1:1-2</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12790,12 +12790,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:2-3</t>
+          <t>North Lilly:9:1:2-3</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:3-4</t>
+          <t>North Lilly:9:1:3-4</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:4-5</t>
+          <t>North Lilly:9:1:4-5</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12946,12 +12946,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:5-7</t>
+          <t>North Lilly:9:1:5-7</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:7-9</t>
+          <t>North Lilly:9:1:7-9</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -13050,12 +13050,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:9-11</t>
+          <t>North Lilly:9:1:9-11</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:11-13</t>
+          <t>North Lilly:9:1:11-13</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:13-15</t>
+          <t>North Lilly:9:1:13-15</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:15-17</t>
+          <t>North Lilly:9:1:15-17</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:17-19</t>
+          <t>North Lilly:9:1:17-19</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13310,12 +13310,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:19-21</t>
+          <t>North Lilly:9:1:19-21</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13362,12 +13362,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:21-23</t>
+          <t>North Lilly:9:1:21-23</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:16:23-25</t>
+          <t>North Lilly:9:1:23-25</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13466,12 +13466,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:0-1</t>
+          <t>North Lilly:9:2:0-1</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13518,12 +13518,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:1-2</t>
+          <t>North Lilly:9:2:1-2</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:2-3</t>
+          <t>North Lilly:9:2:2-3</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13622,12 +13622,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:3-4</t>
+          <t>North Lilly:9:2:3-4</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:4-5</t>
+          <t>North Lilly:9:2:4-5</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13726,12 +13726,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:5-7</t>
+          <t>North Lilly:9:2:5-7</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:7-9</t>
+          <t>North Lilly:9:2:7-9</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:9-11</t>
+          <t>North Lilly:9:2:9-11</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13882,12 +13882,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:11-13</t>
+          <t>North Lilly:9:2:11-13</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13934,12 +13934,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:13-15</t>
+          <t>North Lilly:9:2:13-15</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:15-17</t>
+          <t>North Lilly:9:2:15-17</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -14038,12 +14038,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:17-19</t>
+          <t>North Lilly:9:2:17-19</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -14090,12 +14090,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:19-21</t>
+          <t>North Lilly:9:2:19-21</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -14142,12 +14142,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:21-23</t>
+          <t>North Lilly:9:2:21-23</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>North Lilly:17:23-25</t>
+          <t>North Lilly:9:2:23-25</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -14246,12 +14246,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:0-1</t>
+          <t>Conservation Reserve Program Wetland:10:1:0-1</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14298,12 +14298,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:1-2</t>
+          <t>Conservation Reserve Program Wetland:10:1:1-2</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14350,12 +14350,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:2-3</t>
+          <t>Conservation Reserve Program Wetland:10:1:2-3</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:3-4</t>
+          <t>Conservation Reserve Program Wetland:10:1:3-4</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:4-5</t>
+          <t>Conservation Reserve Program Wetland:10:1:4-5</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14506,12 +14506,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:5-7</t>
+          <t>Conservation Reserve Program Wetland:10:1:5-7</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -14558,12 +14558,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:7-9</t>
+          <t>Conservation Reserve Program Wetland:10:1:7-9</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14610,12 +14610,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:9-11</t>
+          <t>Conservation Reserve Program Wetland:10:1:9-11</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -14662,12 +14662,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:11-13</t>
+          <t>Conservation Reserve Program Wetland:10:1:11-13</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:13-15</t>
+          <t>Conservation Reserve Program Wetland:10:1:13-15</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -14766,12 +14766,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:15-17</t>
+          <t>Conservation Reserve Program Wetland:10:1:15-17</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:18:17-19</t>
+          <t>Conservation Reserve Program Wetland:10:1:17-19</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -14870,12 +14870,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:0-1</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:0-1</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -14922,12 +14922,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:1-2</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:1-2</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -14974,12 +14974,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:2-3</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:2-3</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -15026,12 +15026,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:3-4</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:3-4</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -15078,12 +15078,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:4-5</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:4-5</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -15130,12 +15130,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:5-7</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:5-7</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -15182,12 +15182,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:7-9</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:7-9</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:9-11</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:9-11</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -15286,12 +15286,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:11-13</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:11-13</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -15338,12 +15338,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:13-15</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:13-15</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -15390,12 +15390,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:15-17</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:15-17</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -15442,12 +15442,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:17-19</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:17-19</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -15494,12 +15494,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:19-21</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:19-21</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -15546,12 +15546,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:21-23</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:21-23</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -15598,12 +15598,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:23-25</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:23-25</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -15650,12 +15650,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:25-27</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:25-27</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Enhancement Program Wetland:19:27-29</t>
+          <t>Conservation Reserve Enhancement Program Wetland:11:1:27-29</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -15754,12 +15754,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:0-1</t>
+          <t>Conservation Reserve Program Wetland:12:1:0-1</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -15806,12 +15806,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:1-2</t>
+          <t>Conservation Reserve Program Wetland:12:1:1-2</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:2-3</t>
+          <t>Conservation Reserve Program Wetland:12:1:2-3</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -15910,12 +15910,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:3-4</t>
+          <t>Conservation Reserve Program Wetland:12:1:3-4</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -15962,12 +15962,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:4-5</t>
+          <t>Conservation Reserve Program Wetland:12:1:4-5</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:5-7</t>
+          <t>Conservation Reserve Program Wetland:12:1:5-7</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -16066,12 +16066,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:7-9</t>
+          <t>Conservation Reserve Program Wetland:12:1:7-9</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:9-11</t>
+          <t>Conservation Reserve Program Wetland:12:1:9-11</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -16170,12 +16170,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:11-13</t>
+          <t>Conservation Reserve Program Wetland:12:1:11-13</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:13-15</t>
+          <t>Conservation Reserve Program Wetland:12:1:13-15</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:15-17</t>
+          <t>Conservation Reserve Program Wetland:12:1:15-17</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:17-19</t>
+          <t>Conservation Reserve Program Wetland:12:1:17-19</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -16378,12 +16378,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:19-21</t>
+          <t>Conservation Reserve Program Wetland:12:1:19-21</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -16430,12 +16430,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:21-23</t>
+          <t>Conservation Reserve Program Wetland:12:1:21-23</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -16482,12 +16482,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:23-25</t>
+          <t>Conservation Reserve Program Wetland:12:1:23-25</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -16534,12 +16534,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:25-27</t>
+          <t>Conservation Reserve Program Wetland:12:1:25-27</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -16586,12 +16586,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:20:27-29</t>
+          <t>Conservation Reserve Program Wetland:12:1:27-29</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:0-2</t>
+          <t>Conservation Reserve Program Wetland:13:1:0-2</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -16690,12 +16690,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:2-4</t>
+          <t>Conservation Reserve Program Wetland:13:1:2-4</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -16742,12 +16742,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:4-6</t>
+          <t>Conservation Reserve Program Wetland:13:1:4-6</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:6-8</t>
+          <t>Conservation Reserve Program Wetland:13:1:6-8</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -16846,12 +16846,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:8-10</t>
+          <t>Conservation Reserve Program Wetland:13:1:8-10</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -16898,12 +16898,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:10-12</t>
+          <t>Conservation Reserve Program Wetland:13:1:10-12</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -16950,12 +16950,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:12-14</t>
+          <t>Conservation Reserve Program Wetland:13:1:12-14</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -17002,12 +17002,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:14-16</t>
+          <t>Conservation Reserve Program Wetland:13:1:14-16</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -17054,12 +17054,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:16-18</t>
+          <t>Conservation Reserve Program Wetland:13:1:16-18</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -17106,12 +17106,12 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:18-20</t>
+          <t>Conservation Reserve Program Wetland:13:1:18-20</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -17158,12 +17158,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:20-22</t>
+          <t>Conservation Reserve Program Wetland:13:1:20-22</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -17210,12 +17210,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:22-24</t>
+          <t>Conservation Reserve Program Wetland:13:1:22-24</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -17262,12 +17262,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:24-26</t>
+          <t>Conservation Reserve Program Wetland:13:1:24-26</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:26-28</t>
+          <t>Conservation Reserve Program Wetland:13:1:26-28</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -17366,12 +17366,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:28-30</t>
+          <t>Conservation Reserve Program Wetland:13:1:28-30</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -17418,12 +17418,12 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:30-32</t>
+          <t>Conservation Reserve Program Wetland:13:1:30-32</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -17470,12 +17470,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:32-34</t>
+          <t>Conservation Reserve Program Wetland:13:1:32-34</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -17522,12 +17522,12 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:34-36</t>
+          <t>Conservation Reserve Program Wetland:13:1:34-36</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -17574,12 +17574,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:36-38</t>
+          <t>Conservation Reserve Program Wetland:13:1:36-38</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -17626,12 +17626,12 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:21:38-40</t>
+          <t>Conservation Reserve Program Wetland:13:1:38-40</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -17678,12 +17678,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:0-2</t>
+          <t>Conservation Reserve Program Wetland:14:1:0-2</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -17730,12 +17730,12 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:2-4</t>
+          <t>Conservation Reserve Program Wetland:14:1:2-4</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -17782,12 +17782,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:4-6</t>
+          <t>Conservation Reserve Program Wetland:14:1:4-6</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -17834,12 +17834,12 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:6-8</t>
+          <t>Conservation Reserve Program Wetland:14:1:6-8</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -17886,12 +17886,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:8-10</t>
+          <t>Conservation Reserve Program Wetland:14:1:8-10</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -17938,12 +17938,12 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:10-12</t>
+          <t>Conservation Reserve Program Wetland:14:1:10-12</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -17990,12 +17990,12 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:12-14</t>
+          <t>Conservation Reserve Program Wetland:14:1:12-14</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -18042,12 +18042,12 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:14-16</t>
+          <t>Conservation Reserve Program Wetland:14:1:14-16</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -18094,12 +18094,12 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:16-18</t>
+          <t>Conservation Reserve Program Wetland:14:1:16-18</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -18146,12 +18146,12 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:18-20</t>
+          <t>Conservation Reserve Program Wetland:14:1:18-20</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -18198,12 +18198,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:20-22</t>
+          <t>Conservation Reserve Program Wetland:14:1:20-22</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -18250,12 +18250,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:22-24</t>
+          <t>Conservation Reserve Program Wetland:14:1:22-24</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -18302,12 +18302,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:24-26</t>
+          <t>Conservation Reserve Program Wetland:14:1:24-26</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:26-28</t>
+          <t>Conservation Reserve Program Wetland:14:1:26-28</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -18406,12 +18406,12 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:28-30</t>
+          <t>Conservation Reserve Program Wetland:14:1:28-30</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -18458,12 +18458,12 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:30-32</t>
+          <t>Conservation Reserve Program Wetland:14:1:30-32</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -18510,12 +18510,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:32-34</t>
+          <t>Conservation Reserve Program Wetland:14:1:32-34</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -18562,12 +18562,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:34-36</t>
+          <t>Conservation Reserve Program Wetland:14:1:34-36</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -18614,12 +18614,12 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:36-38</t>
+          <t>Conservation Reserve Program Wetland:14:1:36-38</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -18666,12 +18666,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Conservation Reserve Program Wetland:22:38-40</t>
+          <t>Conservation Reserve Program Wetland:14:1:38-40</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:Core Location ID:Core Number:depth</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
